--- a/code/output/sites/TXAD0405/TXAD0405_BOM_REV1.xlsx
+++ b/code/output/sites/TXAD0405/TXAD0405_BOM_REV1.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>RC-REV0-ERR</t>
+          <t>RC-FIELD-COND</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>RC-REV0-ERR</t>
+          <t>RC-FIELD-COND</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>RC-REV0-ERR</t>
+          <t>RC-FIELD-COND</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>RC-REV0-ERR</t>
+          <t>RC-FIELD-COND</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>RC-RULE-APPLIED</t>
+          <t>RC-REV0-ERR</t>
         </is>
       </c>
     </row>
@@ -6290,46 +6290,46 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Harger</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>GK-6-TW</t>
+          <t>PSU 3000 48V</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>HGR-GK6TW-SYN</t>
+          <t>BML 909 401/1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>CA-161733</t>
+          <t>CA-901123</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ground kit, #6 AWG, two-hole lug, 10 ft</t>
+          <t>Rectifier module, -48 VDC, 3 kW</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>KIT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>VFM</t>
+          <t>CFM</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>CD E-1</t>
+          <t>RFDS R3 Baseband &amp; Power</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>R-OVP-01</t>
+          <t>R-PWR-01</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6384,51 +6384,51 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Power &amp; Grounding</t>
+          <t>Ancillary</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>Thomas &amp; Betts</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>PSU 3000 48V</t>
+          <t>CT-UV-100</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BML 909 401/1</t>
+          <t>TB-CTUV100-SYN</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>CA-901123</t>
+          <t>CA-250671</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Rectifier module, -48 VDC, 3 kW</t>
+          <t>Cable ties, UV-resistant, 100-pack</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CFM</t>
+          <t>VFM</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>RFDS R3 Baseband &amp; Power</t>
+          <t>Customer standard</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>R-PWR-01</t>
+          <t>R-SITE-01</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6488,42 +6488,42 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thomas &amp; Betts</t>
+          <t>Site Pro 1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>CT-UV-100</t>
+          <t>HW-SS-KIT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TB-CTUV100-SYN</t>
+          <t>SP1-HWSS-SYN</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>CA-250671</t>
+          <t>CA-578837</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Cable ties, UV-resistant, 100-pack</t>
+          <t>Stainless hardware kit (bolts, nuts, washers)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>R-SITE-01</t>
+          <t>R-SITE-02</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -6587,27 +6587,27 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Site Pro 1</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>HW-SS-KIT</t>
+          <t>HS-KIT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SP1-HWSS-SYN</t>
+          <t>TE-HSKIT-SYN</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>CA-578837</t>
+          <t>CA-558814</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Stainless hardware kit (bolts, nuts, washers)</t>
+          <t>Heat-shrink kit, assorted</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>R-SITE-02</t>
+          <t>R-SITE-03</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -6686,42 +6686,42 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>HS-KIT</t>
+          <t>LBL-SET-RF</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TE-HSKIT-SYN</t>
+          <t>BRD-LBLRF-SYN</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>CA-558814</t>
+          <t>CA-493243</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Heat-shrink kit, assorted</t>
+          <t>Cable and equipment label set</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>KIT</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="M58" t="n">
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>R-SITE-03</t>
+          <t>R-SITE-04</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -6785,42 +6785,42 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>CommScope</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>LBL-SET-RF</t>
+          <t>WPK-UNIV</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>BRD-LBLRF-SYN</t>
+          <t>WPK-UNIV-SYN</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>CA-493243</t>
+          <t>CA-943565</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Cable and equipment label set</t>
+          <t>Weatherproofing kit (butyl mastic + vinyl tape)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>R-SITE-04</t>
+          <t>R-SITE-05</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -6854,798 +6854,6 @@
       </c>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
-        <is>
-          <t>RC-RULE-APPLIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>TXAD0405</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>DFW</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Ancillary</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>CommScope</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>WPK-UNIV</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>WPK-UNIV-SYN</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>CA-943565</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Weatherproofing kit (butyl mastic + vinyl tape)</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>KIT</t>
-        </is>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>VFM</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Install</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Customer standard</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>R-SITE-05</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>REV 1</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>RC-REV0-ERR</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>TXAD0405</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>DFW</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Fiber &amp; DC</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>CommScope</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>HYB-6x12-100</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>HYB-6X12-100-SYN</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>CA-721411</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Hybrid trunk cable, 6 DC pairs + 12 fiber pairs, 100 ft, factory terminated</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="M61" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>CFM</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Install</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>CD A-4</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>R-TRK-01</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>REV 1</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>RC-RULE-APPLIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>TXAD0405</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>DFW</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Fiber &amp; DC</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Raycap</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>RC-OVP-6-TOP</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>RC-OVP-6T-SYN</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>CA-698253</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>DC surge protection / distribution box, 6-circuit, tower-top</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="M62" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>CFM</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Install</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>CD A-4</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>R-TRK-02</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>REV 1</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>RC-RULE-APPLIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>TXAD0405</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>DFW</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Fiber &amp; DC</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Raycap</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>RC-OVP-6-BASE</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>RC-OVP-6B-SYN</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>CA-160627</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>DC surge protection box, 6-circuit, base</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>CFM</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Install</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>CD A-4</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>R-TRK-03</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>REV 1</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>RC-RULE-APPLIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>TXAD0405</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>DFW</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Ancillary</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>CommScope</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>SNAP-3S</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>SNAP-3S-SYN</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>CA-291571</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Snap-in hanger, 3-stack</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="M64" t="n">
-        <v>34</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>34</v>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>VFM</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Install</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>CD A-4</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>R-TRK-04</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>REV 1</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>RC-RULE-APPLIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>TXAD0405</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>DFW</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Ancillary</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>CommScope</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>HG-125</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>HG-125-SYN</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>CA-301477</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Hoist grip for hybrid cable</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>VFM</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Install</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>CD A-4</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>R-TRK-05</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>REV 1</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>RC-RULE-APPLIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>TXAD0405</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>DFW</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Power &amp; Grounding</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Harger</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>GK-TRK-12</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>HGR-GKTRK-SYN</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>CA-283236</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Trunk ground kit for hybrid cable up to 1.25 in</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>KIT</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>2</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>2</v>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>VFM</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Install</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>CD E-1</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>R-TRK-06</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>REV 1</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>RC-RULE-APPLIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>TXAD0405</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>DFW</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Ancillary</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>CommScope</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>WPK-UNIV</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>WPK-UNIV-SYN</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>CA-943565</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Weatherproofing kit (butyl mastic + vinyl tape)</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>KIT</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>2</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>2</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>VFM</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Install</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Customer standard</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>R-TRK-07</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>REV 1</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr">
         <is>
           <t>RC-REV0-ERR</t>
         </is>
@@ -7662,7 +6870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7734,14 +6942,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RC-REV0-ERR (+2)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>DSC-6B7BF60ADDD9</t>
-        </is>
-      </c>
+          <t>RC-FIELD-COND (+2)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7770,14 +6974,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RC-REV0-ERR (+2)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>DSC-6B7BF60ADDD9</t>
-        </is>
-      </c>
+          <t>RC-FIELD-COND (+2)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7787,29 +6987,281 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>GK6</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Install</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RC-REV0-ERR (-2)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DSC-6F8EFBE9FCA8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GKT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Install</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RC-REV0-ERR (-2)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DSC-0DEA2FC1A9F1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HANGER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Install</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>34</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RC-REV0-ERR (-34)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DSC-711A3897D409</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HOIST</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Install</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RC-REV0-ERR (-1)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DSC-7B96DA8BAC79</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HYB100</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Install</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RC-REV0-ERR (-1)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DSC-BE2479E38342</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OVPB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Install</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RC-REV0-ERR (-1)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DSC-4E3EA02519B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OVPT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Install</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RC-REV0-ERR (-1)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DSC-E45EA5A9C93C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>WPK</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Install</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>RC-REV0-ERR (+3)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RC-REV0-ERR (+1)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>DSC-6B7BF60ADDD9</t>
         </is>
